--- a/dados/Planilha exercícios e infos.xlsx
+++ b/dados/Planilha exercícios e infos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="456">
   <si>
     <t>Exercício</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Halter</t>
   </si>
   <si>
-    <t>Máquina</t>
-  </si>
-  <si>
     <t>Cadeira extensora</t>
   </si>
   <si>
@@ -1065,9 +1062,6 @@
     <t>Leg press horizontal</t>
   </si>
   <si>
-    <t>Supino articulado</t>
-  </si>
-  <si>
     <t>Banco romano</t>
   </si>
   <si>
@@ -1086,9 +1080,6 @@
     <t>Paralelas Máquina</t>
   </si>
   <si>
-    <t>maquina paralelas</t>
-  </si>
-  <si>
     <t>Glúteo</t>
   </si>
   <si>
@@ -1366,6 +1357,36 @@
   </si>
   <si>
     <t>https://www.youtube.com/shorts/0sykOmp6jBk</t>
+  </si>
+  <si>
+    <t>Mesa Flexora</t>
+  </si>
+  <si>
+    <t>Supino inclinado/Barra</t>
+  </si>
+  <si>
+    <t>Supino reto/Barra</t>
+  </si>
+  <si>
+    <t>Supino declinado/Barra</t>
+  </si>
+  <si>
+    <t>Banco/Halter</t>
+  </si>
+  <si>
+    <t>Banco scott/Barra</t>
+  </si>
+  <si>
+    <t>Máquina paralelas</t>
+  </si>
+  <si>
+    <t>Cadeira Adutora</t>
+  </si>
+  <si>
+    <t>Máquina abdominal</t>
+  </si>
+  <si>
+    <t>Remada baixa</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1733,7 @@
     <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
@@ -1730,49 +1751,49 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
         <v>120</v>
       </c>
-      <c r="C1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>121</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>122</v>
       </c>
-      <c r="I1" t="s">
-        <v>123</v>
-      </c>
       <c r="J1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" t="s">
         <v>76</v>
       </c>
-      <c r="L1" t="s">
-        <v>96</v>
-      </c>
-      <c r="M1" t="s">
-        <v>77</v>
-      </c>
       <c r="N1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1780,19 +1801,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1807,22 +1828,22 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1830,19 +1851,19 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1857,42 +1878,42 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1907,39 +1928,39 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1954,86 +1975,86 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" t="s">
+        <v>94</v>
+      </c>
+      <c r="M7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7" t="s">
+        <v>150</v>
+      </c>
+      <c r="P7" t="s">
         <v>278</v>
-      </c>
-      <c r="F7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>95</v>
-      </c>
-      <c r="L7" t="s">
-        <v>95</v>
-      </c>
-      <c r="M7" t="s">
-        <v>95</v>
-      </c>
-      <c r="O7" t="s">
-        <v>151</v>
-      </c>
-      <c r="P7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -2048,39 +2069,39 @@
         <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -2095,19 +2116,19 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -2115,19 +2136,19 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2142,42 +2163,42 @@
         <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2192,39 +2213,39 @@
         <v>5</v>
       </c>
       <c r="K11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -2239,42 +2260,42 @@
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2289,39 +2310,39 @@
         <v>5</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -2336,42 +2357,42 @@
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -2386,39 +2407,39 @@
         <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -2433,39 +2454,39 @@
         <v>3</v>
       </c>
       <c r="K16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -2480,39 +2501,39 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -2527,39 +2548,39 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="B19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>446</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2574,39 +2595,39 @@
         <v>5</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>446</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -2621,42 +2642,42 @@
         <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P20" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>446</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -2671,42 +2692,42 @@
         <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P21" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2721,39 +2742,39 @@
         <v>5</v>
       </c>
       <c r="K22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -2768,42 +2789,42 @@
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -2818,36 +2839,36 @@
         <v>3</v>
       </c>
       <c r="K24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>3</v>
@@ -2862,39 +2883,39 @@
         <v>3</v>
       </c>
       <c r="K25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2909,42 +2930,42 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2959,42 +2980,42 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P27" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -3009,39 +3030,39 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3056,42 +3077,42 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P29" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
         <v>54</v>
       </c>
-      <c r="B30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s">
         <v>55</v>
       </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
       <c r="F30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3106,39 +3127,39 @@
         <v>5</v>
       </c>
       <c r="K30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3153,39 +3174,39 @@
         <v>3</v>
       </c>
       <c r="K31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3200,39 +3221,39 @@
         <v>3</v>
       </c>
       <c r="K32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P32" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -3247,39 +3268,39 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E34" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -3294,39 +3315,39 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -3341,39 +3362,39 @@
         <v>5</v>
       </c>
       <c r="K35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -3388,39 +3409,39 @@
         <v>3</v>
       </c>
       <c r="K36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -3435,39 +3456,39 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -3482,42 +3503,42 @@
         <v>2</v>
       </c>
       <c r="K38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -3532,42 +3553,42 @@
         <v>2</v>
       </c>
       <c r="K39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -3582,42 +3603,42 @@
         <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P40" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -3632,39 +3653,39 @@
         <v>5</v>
       </c>
       <c r="K41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P41" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -3679,39 +3700,39 @@
         <v>5</v>
       </c>
       <c r="K42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P42" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G43">
         <v>5</v>
@@ -3726,39 +3747,39 @@
         <v>5</v>
       </c>
       <c r="K43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -3773,39 +3794,39 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P44" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -3820,39 +3841,39 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P45" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" t="s">
         <v>18</v>
       </c>
-      <c r="B46" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E46" t="s">
-        <v>3</v>
+        <v>448</v>
       </c>
       <c r="F46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -3867,39 +3888,39 @@
         <v>4</v>
       </c>
       <c r="K46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P46" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E47" t="s">
-        <v>3</v>
+        <v>447</v>
       </c>
       <c r="F47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -3914,39 +3935,39 @@
         <v>4</v>
       </c>
       <c r="K47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P47" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E48" t="s">
-        <v>3</v>
+        <v>449</v>
       </c>
       <c r="F48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -3961,36 +3982,36 @@
         <v>2</v>
       </c>
       <c r="K48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
-        <v>348</v>
+        <v>450</v>
       </c>
       <c r="F49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -4005,39 +4026,39 @@
         <v>3</v>
       </c>
       <c r="K49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -4052,39 +4073,39 @@
         <v>5</v>
       </c>
       <c r="K50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P50" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -4099,39 +4120,39 @@
         <v>5</v>
       </c>
       <c r="K51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="F52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G52">
         <v>4</v>
@@ -4146,39 +4167,39 @@
         <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G53">
         <v>4</v>
@@ -4193,39 +4214,39 @@
         <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -4240,39 +4261,39 @@
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P54" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -4287,39 +4308,39 @@
         <v>3</v>
       </c>
       <c r="K55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P55" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
       </c>
       <c r="F56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G56">
         <v>2</v>
@@ -4334,39 +4355,39 @@
         <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G57">
         <v>3</v>
@@ -4381,39 +4402,39 @@
         <v>3</v>
       </c>
       <c r="K57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P57" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" t="s">
         <v>26</v>
       </c>
-      <c r="B58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" t="s">
-        <v>27</v>
-      </c>
       <c r="D58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E58" t="s">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -4428,42 +4449,42 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N58" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P58" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
       </c>
       <c r="F59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G59">
         <v>4</v>
@@ -4478,42 +4499,42 @@
         <v>4</v>
       </c>
       <c r="K59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P59" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E60" t="s">
         <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G60">
         <v>5</v>
@@ -4528,39 +4549,39 @@
         <v>5</v>
       </c>
       <c r="K60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O60" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P60" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -4575,39 +4596,39 @@
         <v>5</v>
       </c>
       <c r="K61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O61" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P61" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
       </c>
       <c r="F62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -4622,39 +4643,39 @@
         <v>3</v>
       </c>
       <c r="K62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O62" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P62" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -4669,39 +4690,39 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P63" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" t="s">
         <v>31</v>
       </c>
-      <c r="B64" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" t="s">
-        <v>32</v>
-      </c>
       <c r="D64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E64" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G64">
         <v>3</v>
@@ -4716,39 +4737,39 @@
         <v>3</v>
       </c>
       <c r="K64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P64" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E65" t="s">
         <v>7</v>
       </c>
       <c r="F65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -4763,39 +4784,39 @@
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E66" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -4810,36 +4831,36 @@
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O66" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E67" t="s">
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G67">
         <v>3</v>
@@ -4854,39 +4875,39 @@
         <v>3</v>
       </c>
       <c r="K67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P67" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G68">
         <v>3</v>
@@ -4901,36 +4922,36 @@
         <v>3</v>
       </c>
       <c r="K68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O68" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G69">
         <v>3</v>
@@ -4945,39 +4966,39 @@
         <v>3</v>
       </c>
       <c r="K69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O69" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P69" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E70" t="s">
         <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G70">
         <v>3</v>
@@ -4992,36 +5013,36 @@
         <v>3</v>
       </c>
       <c r="K70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O70" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>337</v>
       </c>
       <c r="F71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G71">
         <v>5</v>
@@ -5036,39 +5057,39 @@
         <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P71" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G72">
         <v>3</v>
@@ -5083,39 +5104,39 @@
         <v>3</v>
       </c>
       <c r="K72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O72" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P72" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E73" t="s">
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G73">
         <v>3</v>
@@ -5130,39 +5151,39 @@
         <v>3</v>
       </c>
       <c r="K73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P73" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E74" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -5177,39 +5198,39 @@
         <v>3</v>
       </c>
       <c r="K74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O74" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P74" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>336</v>
+      </c>
+      <c r="B75" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" t="s">
         <v>337</v>
       </c>
-      <c r="B75" t="s">
-        <v>133</v>
-      </c>
-      <c r="C75" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" t="s">
-        <v>95</v>
-      </c>
-      <c r="E75" t="s">
-        <v>338</v>
-      </c>
       <c r="F75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G75">
         <v>3</v>
@@ -5224,39 +5245,39 @@
         <v>3</v>
       </c>
       <c r="K75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O75" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P75" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76">
         <v>3</v>
@@ -5271,39 +5292,39 @@
         <v>3</v>
       </c>
       <c r="K76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O76" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B77" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77">
         <v>3</v>
@@ -5318,39 +5339,39 @@
         <v>3</v>
       </c>
       <c r="K77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O77" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P77" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B78" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78">
         <v>3</v>
@@ -5365,39 +5386,39 @@
         <v>3</v>
       </c>
       <c r="K78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O78" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P78" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E79" t="s">
-        <v>23</v>
+        <v>455</v>
       </c>
       <c r="F79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G79">
         <v>3</v>
@@ -5412,39 +5433,39 @@
         <v>3</v>
       </c>
       <c r="K79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O79" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B80" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E80" t="s">
-        <v>23</v>
+        <v>455</v>
       </c>
       <c r="F80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G80">
         <v>3</v>
@@ -5459,39 +5480,39 @@
         <v>3</v>
       </c>
       <c r="K80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E81" t="s">
-        <v>23</v>
+        <v>455</v>
       </c>
       <c r="F81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -5506,39 +5527,39 @@
         <v>3</v>
       </c>
       <c r="K81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O81" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P81" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>455</v>
       </c>
       <c r="F82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G82">
         <v>3</v>
@@ -5553,39 +5574,39 @@
         <v>3</v>
       </c>
       <c r="K82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O82" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P82" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B83" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -5600,39 +5621,39 @@
         <v>3</v>
       </c>
       <c r="K83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O83" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B84" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E84" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G84">
         <v>3</v>
@@ -5647,39 +5668,39 @@
         <v>3</v>
       </c>
       <c r="K84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O84" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G85">
         <v>3</v>
@@ -5694,39 +5715,39 @@
         <v>3</v>
       </c>
       <c r="K85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O85" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B86" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G86">
         <v>3</v>
@@ -5741,39 +5762,39 @@
         <v>3</v>
       </c>
       <c r="K86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O86" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C87" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E87" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G87">
         <v>3</v>
@@ -5788,39 +5809,39 @@
         <v>3</v>
       </c>
       <c r="K87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O87" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G88">
         <v>3</v>
@@ -5835,39 +5856,39 @@
         <v>3</v>
       </c>
       <c r="K88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O88" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G89">
         <v>3</v>
@@ -5882,39 +5903,39 @@
         <v>3</v>
       </c>
       <c r="K89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O89" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E90" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="F90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G90">
         <v>3</v>
@@ -5929,36 +5950,36 @@
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O90" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>38</v>
+      </c>
+      <c r="B91" t="s">
+        <v>135</v>
+      </c>
+      <c r="C91" t="s">
         <v>39</v>
       </c>
-      <c r="B91" t="s">
-        <v>136</v>
-      </c>
-      <c r="C91" t="s">
-        <v>40</v>
-      </c>
       <c r="D91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E91" t="s">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G91">
         <v>4</v>
@@ -5973,39 +5994,39 @@
         <v>4</v>
       </c>
       <c r="K91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O91" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P91" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E92" t="s">
         <v>7</v>
       </c>
       <c r="F92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G92">
         <v>4</v>
@@ -6020,39 +6041,39 @@
         <v>4</v>
       </c>
       <c r="K92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O92" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
       </c>
       <c r="F93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G93">
         <v>4</v>
@@ -6067,39 +6088,39 @@
         <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E94" t="s">
         <v>7</v>
       </c>
       <c r="F94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G94">
         <v>2</v>
@@ -6114,39 +6135,39 @@
         <v>3</v>
       </c>
       <c r="K94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O94" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P94" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E95" t="s">
         <v>7</v>
       </c>
       <c r="F95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G95">
         <v>2</v>
@@ -6161,39 +6182,39 @@
         <v>3</v>
       </c>
       <c r="K95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O95" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B96" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E96" t="s">
         <v>7</v>
       </c>
       <c r="F96" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G96">
         <v>2</v>
@@ -6208,39 +6229,39 @@
         <v>3</v>
       </c>
       <c r="K96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O96" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P96" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B97" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
       </c>
       <c r="F97" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G97">
         <v>2</v>
@@ -6255,39 +6276,39 @@
         <v>3</v>
       </c>
       <c r="K97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O97" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B98" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E98" t="s">
         <v>7</v>
       </c>
       <c r="F98" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G98">
         <v>2</v>
@@ -6302,39 +6323,39 @@
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O98" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E99" t="s">
         <v>7</v>
       </c>
       <c r="F99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G99">
         <v>2</v>
@@ -6349,39 +6370,39 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O99" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P99" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E100" t="s">
-        <v>3</v>
+        <v>451</v>
       </c>
       <c r="F100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G100">
         <v>4</v>
@@ -6396,39 +6417,39 @@
         <v>3</v>
       </c>
       <c r="K100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O100" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P100" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G101">
         <v>2</v>
@@ -6443,39 +6464,39 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O101" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P101" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B102" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C102" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E102" t="s">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G102">
         <v>4</v>
@@ -6490,86 +6511,86 @@
         <v>4</v>
       </c>
       <c r="K102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P102" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>217</v>
+      </c>
+      <c r="B103" t="s">
+        <v>135</v>
+      </c>
+      <c r="C103" t="s">
+        <v>78</v>
+      </c>
+      <c r="D103" t="s">
+        <v>94</v>
+      </c>
+      <c r="E103" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" t="s">
+        <v>79</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="K103" t="s">
+        <v>94</v>
+      </c>
+      <c r="L103" t="s">
+        <v>94</v>
+      </c>
+      <c r="M103" t="s">
+        <v>94</v>
+      </c>
+      <c r="O103" t="s">
+        <v>150</v>
+      </c>
+      <c r="P103" t="s">
         <v>218</v>
-      </c>
-      <c r="B103" t="s">
-        <v>136</v>
-      </c>
-      <c r="C103" t="s">
-        <v>79</v>
-      </c>
-      <c r="D103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E103" t="s">
-        <v>23</v>
-      </c>
-      <c r="F103" t="s">
-        <v>80</v>
-      </c>
-      <c r="G103">
-        <v>2</v>
-      </c>
-      <c r="H103">
-        <v>1</v>
-      </c>
-      <c r="I103">
-        <v>1</v>
-      </c>
-      <c r="J103">
-        <v>2</v>
-      </c>
-      <c r="K103" t="s">
-        <v>95</v>
-      </c>
-      <c r="L103" t="s">
-        <v>95</v>
-      </c>
-      <c r="M103" t="s">
-        <v>95</v>
-      </c>
-      <c r="O103" t="s">
-        <v>151</v>
-      </c>
-      <c r="P103" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B104" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E104" t="s">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G104">
         <v>4</v>
@@ -6584,36 +6605,36 @@
         <v>4</v>
       </c>
       <c r="K104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O104" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E105" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F105" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G105">
         <v>5</v>
@@ -6628,39 +6649,39 @@
         <v>5</v>
       </c>
       <c r="K105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O105" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P105" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F106" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G106">
         <v>2</v>
@@ -6675,39 +6696,39 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L106" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M106" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P106" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E107" t="s">
-        <v>355</v>
+        <v>452</v>
       </c>
       <c r="F107" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -6722,39 +6743,39 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L107" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M107" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P107" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B108" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F108" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G108">
         <v>3</v>
@@ -6769,39 +6790,39 @@
         <v>3</v>
       </c>
       <c r="K108" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L108" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M108" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O108" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P108" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D109" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F109" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G109">
         <v>3</v>
@@ -6816,39 +6837,39 @@
         <v>3</v>
       </c>
       <c r="K109" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L109" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M109" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P109" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G110">
         <v>3</v>
@@ -6863,39 +6884,39 @@
         <v>3</v>
       </c>
       <c r="K110" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L110" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M110" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O110" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P110" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B111" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D111" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G111">
         <v>3</v>
@@ -6910,39 +6931,39 @@
         <v>3</v>
       </c>
       <c r="K111" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L111" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M111" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O111" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P111" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B112" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E112" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F112" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G112">
         <v>3</v>
@@ -6957,39 +6978,39 @@
         <v>3</v>
       </c>
       <c r="K112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O112" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P112" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B113" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E113" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F113" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G113">
         <v>3</v>
@@ -7004,39 +7025,39 @@
         <v>3</v>
       </c>
       <c r="K113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O113" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P113" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B114" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F114" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G114">
         <v>4</v>
@@ -7051,39 +7072,39 @@
         <v>4</v>
       </c>
       <c r="K114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L114" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P114" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B115" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C115" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G115">
         <v>5</v>
@@ -7098,39 +7119,39 @@
         <v>5</v>
       </c>
       <c r="K115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P115" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C116" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D116" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F116" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G116">
         <v>5</v>
@@ -7145,42 +7166,42 @@
         <v>5</v>
       </c>
       <c r="K116" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L116" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M116" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O116" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P116" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B117" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E117" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F117" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G117">
         <v>5</v>
@@ -7195,39 +7216,39 @@
         <v>5</v>
       </c>
       <c r="K117" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L117" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M117" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O117" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P117" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C118" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D118" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F118" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -7242,39 +7263,39 @@
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L118" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M118" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O118" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P118" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B119" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C119" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D119" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -7289,39 +7310,39 @@
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L119" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M119" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C120" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D120" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E120" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F120" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G120">
         <v>4</v>
@@ -7336,39 +7357,39 @@
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L120" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M120" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O120" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P120" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C121" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G121">
         <v>5</v>
@@ -7383,39 +7404,39 @@
         <v>5</v>
       </c>
       <c r="K121" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L121" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M121" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O121" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>47</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122" t="s">
         <v>48</v>
       </c>
-      <c r="B122" t="s">
-        <v>134</v>
-      </c>
-      <c r="C122" t="s">
-        <v>49</v>
-      </c>
       <c r="D122" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F122" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G122">
         <v>5</v>
@@ -7430,39 +7451,39 @@
         <v>5</v>
       </c>
       <c r="K122" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L122" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M122" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O122" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P122" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C123" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D123" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F123" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G123">
         <v>5</v>
@@ -7477,39 +7498,39 @@
         <v>5</v>
       </c>
       <c r="K123" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L123" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M123" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O123" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P123" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C124" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D124" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F124" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G124">
         <v>4</v>
@@ -7524,39 +7545,39 @@
         <v>4</v>
       </c>
       <c r="K124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M124" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O124" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P124" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C125" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D125" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E125" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F125" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G125">
         <v>4</v>
@@ -7571,39 +7592,39 @@
         <v>4</v>
       </c>
       <c r="K125" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L125" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M125" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O125" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P125" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C126" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D126" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G126">
         <v>5</v>
@@ -7618,39 +7639,39 @@
         <v>5</v>
       </c>
       <c r="K126" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L126" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M126" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O126" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B127" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F127" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G127">
         <v>5</v>
@@ -7665,39 +7686,39 @@
         <v>5</v>
       </c>
       <c r="K127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O127" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C128" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D128" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F128" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G128">
         <v>5</v>
@@ -7712,39 +7733,39 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L128" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M128" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O128" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P128" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F129" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G129">
         <v>5</v>
@@ -7759,39 +7780,39 @@
         <v>5</v>
       </c>
       <c r="K129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O129" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G130">
         <v>5</v>
@@ -7806,39 +7827,39 @@
         <v>5</v>
       </c>
       <c r="K130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O130" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P130" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B131" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C131" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F131" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G131">
         <v>5</v>
@@ -7853,39 +7874,39 @@
         <v>5</v>
       </c>
       <c r="K131" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L131" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M131" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O131" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P131" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B132" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C132" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D132" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F132" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G132">
         <v>5</v>
@@ -7900,39 +7921,39 @@
         <v>5</v>
       </c>
       <c r="K132" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L132" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M132" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O132" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P132" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B133" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C133" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D133" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E133" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F133" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G133">
         <v>5</v>
@@ -7947,39 +7968,39 @@
         <v>4</v>
       </c>
       <c r="K133" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L133" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M133" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O133" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C134" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D134" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E134" t="s">
-        <v>38</v>
+        <v>339</v>
       </c>
       <c r="F134" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G134">
         <v>2</v>
@@ -7994,39 +8015,39 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L134" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M134" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N134" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P134" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D135" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E135" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F135" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G135">
         <v>2</v>
@@ -8041,42 +8062,42 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L135" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M135" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N135" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O135" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P135" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C136" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G136">
         <v>5</v>
@@ -8091,39 +8112,39 @@
         <v>5</v>
       </c>
       <c r="K136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M136" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O136" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P136" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C137" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E137" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F137" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G137">
         <v>5</v>
@@ -8138,39 +8159,39 @@
         <v>5</v>
       </c>
       <c r="K137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M137" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O137" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P137" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B138" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C138" t="s">
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E138" t="s">
-        <v>8</v>
+        <v>453</v>
       </c>
       <c r="F138" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G138">
         <v>5</v>
@@ -8185,39 +8206,39 @@
         <v>5</v>
       </c>
       <c r="K138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M138" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O138" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P138" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B139" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D139" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E139" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F139" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G139">
         <v>4</v>
@@ -8232,39 +8253,39 @@
         <v>4</v>
       </c>
       <c r="K139" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L139" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M139" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O139" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P139" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C140" t="s">
         <v>2</v>
       </c>
       <c r="D140" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E140" t="s">
         <v>7</v>
       </c>
       <c r="F140" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G140">
         <v>3</v>
@@ -8279,86 +8300,86 @@
         <v>3</v>
       </c>
       <c r="K140" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L140" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M140" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O140" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P140" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B141" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C141" t="s">
         <v>2</v>
       </c>
       <c r="D141" t="s">
+        <v>92</v>
+      </c>
+      <c r="E141" t="s">
+        <v>56</v>
+      </c>
+      <c r="F141" t="s">
+        <v>79</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>2</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141" t="s">
         <v>93</v>
       </c>
-      <c r="E141" t="s">
-        <v>14</v>
-      </c>
-      <c r="F141" t="s">
-        <v>80</v>
-      </c>
-      <c r="G141">
-        <v>1</v>
-      </c>
-      <c r="H141">
-        <v>2</v>
-      </c>
-      <c r="I141">
-        <v>1</v>
-      </c>
-      <c r="J141">
-        <v>1</v>
-      </c>
-      <c r="K141" t="s">
-        <v>94</v>
-      </c>
       <c r="L141" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M141" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P141" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C142" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D142" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -8373,36 +8394,36 @@
         <v>1</v>
       </c>
       <c r="K142" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L142" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M142" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O142" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B143" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D143" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G143">
         <v>3</v>
@@ -8417,39 +8438,39 @@
         <v>3</v>
       </c>
       <c r="K143" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L143" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M143" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O143" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P143" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>60</v>
+      </c>
+      <c r="B144" t="s">
+        <v>128</v>
+      </c>
+      <c r="C144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" t="s">
+        <v>92</v>
+      </c>
+      <c r="E144" t="s">
         <v>61</v>
       </c>
-      <c r="B144" t="s">
-        <v>129</v>
-      </c>
-      <c r="C144" t="s">
-        <v>13</v>
-      </c>
-      <c r="D144" t="s">
-        <v>93</v>
-      </c>
-      <c r="E144" t="s">
-        <v>62</v>
-      </c>
       <c r="F144" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G144">
         <v>3</v>
@@ -8464,39 +8485,39 @@
         <v>3</v>
       </c>
       <c r="K144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L144" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O144" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P144" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B145" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C145" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D145" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E145" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F145" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G145">
         <v>2</v>
@@ -8511,39 +8532,39 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L145" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M145" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O145" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P145" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B146" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C146" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" t="s">
+        <v>94</v>
+      </c>
+      <c r="E146" t="s">
         <v>13</v>
       </c>
-      <c r="D146" t="s">
-        <v>95</v>
-      </c>
-      <c r="E146" t="s">
-        <v>14</v>
-      </c>
       <c r="F146" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G146">
         <v>5</v>
@@ -8558,39 +8579,39 @@
         <v>5</v>
       </c>
       <c r="K146" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L146" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M146" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O146" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P146" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B147" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C147" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E147" t="s">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="F147" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G147">
         <v>5</v>
@@ -8605,39 +8626,39 @@
         <v>5</v>
       </c>
       <c r="K147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O147" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P147" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B148" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C148" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D148" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E148" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F148" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G148">
         <v>4</v>
@@ -8652,39 +8673,39 @@
         <v>4</v>
       </c>
       <c r="K148" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L148" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M148" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O148" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P148" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B149" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E149" t="s">
         <v>7</v>
       </c>
       <c r="F149" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G149">
         <v>3</v>
@@ -8699,39 +8720,39 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O149" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P149" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B150" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D150" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E150" t="s">
         <v>7</v>
       </c>
       <c r="F150" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G150">
         <v>3</v>
@@ -8746,39 +8767,39 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L150" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M150" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O150" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P150" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B151" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C151" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D151" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E151" t="s">
-        <v>8</v>
+        <v>454</v>
       </c>
       <c r="F151" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G151">
         <v>3</v>
@@ -8793,36 +8814,36 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L151" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M151" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O151" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B152" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C152" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D152" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F152" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G152">
         <v>3</v>
@@ -8837,39 +8858,39 @@
         <v>1</v>
       </c>
       <c r="K152" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L152" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M152" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O152" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P152" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B153" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C153" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D153" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F153" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -8884,39 +8905,39 @@
         <v>1</v>
       </c>
       <c r="K153" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L153" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M153" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O153" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P153" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B154" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C154" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D154" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F154" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -8931,39 +8952,39 @@
         <v>1</v>
       </c>
       <c r="K154" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L154" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M154" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P154" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B155" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C155" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D155" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F155" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -8978,39 +8999,39 @@
         <v>1</v>
       </c>
       <c r="K155" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L155" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M155" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P155" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B156" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C156" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D156" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F156" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -9025,39 +9046,39 @@
         <v>1</v>
       </c>
       <c r="K156" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L156" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M156" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P156" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B157" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C157" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D157" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F157" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -9072,39 +9093,39 @@
         <v>1</v>
       </c>
       <c r="K157" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P157" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B158" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C158" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D158" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F158" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -9119,39 +9140,39 @@
         <v>1</v>
       </c>
       <c r="K158" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L158" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M158" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O158" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P158" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B159" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C159" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F159" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G159">
         <v>3</v>
@@ -9166,39 +9187,39 @@
         <v>1</v>
       </c>
       <c r="K159" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O159" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P159" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B160" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C160" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D160" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E160" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F160" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G160">
         <v>3</v>
@@ -9213,39 +9234,39 @@
         <v>1</v>
       </c>
       <c r="K160" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L160" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M160" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P160" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B161" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C161" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D161" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F161" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -9260,39 +9281,39 @@
         <v>1</v>
       </c>
       <c r="K161" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O161" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P161" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B162" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C162" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D162" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E162" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F162" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -9307,124 +9328,124 @@
         <v>1</v>
       </c>
       <c r="K162" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O162" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B163" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C163" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D163" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F163" t="s">
+        <v>84</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>5</v>
+      </c>
+      <c r="I163">
+        <v>5</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163" t="s">
         <v>85</v>
       </c>
-      <c r="G163">
-        <v>1</v>
-      </c>
-      <c r="H163">
-        <v>5</v>
-      </c>
-      <c r="I163">
-        <v>5</v>
-      </c>
-      <c r="J163">
-        <v>1</v>
-      </c>
-      <c r="K163" t="s">
-        <v>86</v>
-      </c>
       <c r="L163" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M163" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O163" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B164" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C164" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D164" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E164" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F164" t="s">
+        <v>84</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164">
+        <v>5</v>
+      </c>
+      <c r="I164">
+        <v>5</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164" t="s">
         <v>85</v>
       </c>
-      <c r="G164">
-        <v>1</v>
-      </c>
-      <c r="H164">
-        <v>5</v>
-      </c>
-      <c r="I164">
-        <v>5</v>
-      </c>
-      <c r="J164">
-        <v>1</v>
-      </c>
-      <c r="K164" t="s">
-        <v>86</v>
-      </c>
       <c r="L164" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M164" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O164" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B165" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C165" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D165" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F165" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -9439,39 +9460,39 @@
         <v>1</v>
       </c>
       <c r="K165" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L165" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M165" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O165" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P165" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B166" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C166" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D166" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -9486,39 +9507,39 @@
         <v>1</v>
       </c>
       <c r="K166" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L166" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M166" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O166" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P166" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B167" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C167" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D167" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F167" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -9533,127 +9554,127 @@
         <v>1</v>
       </c>
       <c r="K167" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L167" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M167" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O167" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P167" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B168" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C168" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F168" t="s">
+        <v>84</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168">
+        <v>5</v>
+      </c>
+      <c r="I168">
+        <v>5</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168" t="s">
         <v>85</v>
       </c>
-      <c r="G168">
-        <v>1</v>
-      </c>
-      <c r="H168">
-        <v>5</v>
-      </c>
-      <c r="I168">
-        <v>5</v>
-      </c>
-      <c r="J168">
-        <v>1</v>
-      </c>
-      <c r="K168" t="s">
-        <v>86</v>
-      </c>
       <c r="L168" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M168" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O168" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B169" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C169" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D169" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F169" t="s">
+        <v>84</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169">
+        <v>5</v>
+      </c>
+      <c r="I169">
+        <v>5</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169" t="s">
         <v>85</v>
       </c>
-      <c r="G169">
-        <v>1</v>
-      </c>
-      <c r="H169">
-        <v>5</v>
-      </c>
-      <c r="I169">
-        <v>5</v>
-      </c>
-      <c r="J169">
-        <v>1</v>
-      </c>
-      <c r="K169" t="s">
-        <v>86</v>
-      </c>
       <c r="L169" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M169" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O169" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B170" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C170" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D170" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E170" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F170" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -9668,39 +9689,39 @@
         <v>1</v>
       </c>
       <c r="K170" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L170" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M170" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O170" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P170" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B171" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C171" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D171" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E171" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F171" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -9715,39 +9736,39 @@
         <v>1</v>
       </c>
       <c r="K171" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L171" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M171" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O171" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P171" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B172" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C172" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D172" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E172" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F172" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -9762,39 +9783,39 @@
         <v>1</v>
       </c>
       <c r="K172" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L172" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M172" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O172" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P172" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B173" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C173" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D173" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E173" t="s">
         <v>3</v>
       </c>
       <c r="F173" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -9809,39 +9830,39 @@
         <v>1</v>
       </c>
       <c r="K173" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L173" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M173" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O173" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P173" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B174" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C174" t="s">
         <v>2</v>
       </c>
       <c r="D174" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F174" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G174">
         <v>2</v>
@@ -9856,39 +9877,39 @@
         <v>2</v>
       </c>
       <c r="K174" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L174" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M174" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O174" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P174" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" t="s">
+        <v>140</v>
+      </c>
+      <c r="C175" t="s">
+        <v>353</v>
+      </c>
+      <c r="D175" t="s">
+        <v>94</v>
+      </c>
+      <c r="E175" t="s">
         <v>15</v>
       </c>
-      <c r="B175" t="s">
-        <v>141</v>
-      </c>
-      <c r="C175" t="s">
-        <v>356</v>
-      </c>
-      <c r="D175" t="s">
-        <v>95</v>
-      </c>
-      <c r="E175" t="s">
-        <v>16</v>
-      </c>
       <c r="F175" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G175">
         <v>4</v>
@@ -9903,42 +9924,42 @@
         <v>4</v>
       </c>
       <c r="K175" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L175" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M175" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N175" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O175" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P175" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B176" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C176" t="s">
         <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E176" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F176" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G176">
         <v>4</v>
@@ -9953,39 +9974,39 @@
         <v>4</v>
       </c>
       <c r="K176" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L176" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M176" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O176" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P176" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B177" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C177" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D177" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E177" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F177" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -10000,39 +10021,39 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L177" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M177" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O177" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P177" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>139</v>
+      </c>
+      <c r="B178" t="s">
         <v>140</v>
       </c>
-      <c r="B178" t="s">
-        <v>141</v>
-      </c>
       <c r="C178" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D178" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E178" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F178" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G178">
         <v>5</v>
@@ -10047,39 +10068,39 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L178" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M178" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O178" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P178" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B179" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C179" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D179" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E179" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F179" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G179">
         <v>5</v>
@@ -10094,39 +10115,39 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L179" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M179" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O179" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P179" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B180" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C180" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D180" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F180" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G180">
         <v>5</v>
@@ -10141,39 +10162,39 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L180" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M180" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O180" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P180" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B181" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C181" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D181" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G181">
         <v>4</v>
@@ -10188,39 +10209,39 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L181" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M181" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O181" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P181" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B182" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C182" t="s">
         <v>2</v>
       </c>
       <c r="D182" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E182" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F182" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G182">
         <v>5</v>
@@ -10235,39 +10256,39 @@
         <v>1</v>
       </c>
       <c r="K182" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L182" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M182" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O182" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P182" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B183" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C183" t="s">
         <v>2</v>
       </c>
       <c r="D183" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E183" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G183">
         <v>3</v>
@@ -10282,39 +10303,39 @@
         <v>1</v>
       </c>
       <c r="K183" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L183" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M183" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O183" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P183" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B184" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C184" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D184" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E184" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F184" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -10329,39 +10350,39 @@
         <v>1</v>
       </c>
       <c r="K184" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L184" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M184" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O184" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C185" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D185" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E185" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -10376,39 +10397,39 @@
         <v>1</v>
       </c>
       <c r="K185" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L185" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M185" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O185" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P185" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B186" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C186" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E186" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F186" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -10423,39 +10444,39 @@
         <v>1</v>
       </c>
       <c r="K186" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L186" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M186" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O186" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B187" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C187" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D187" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E187" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F187" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -10470,39 +10491,39 @@
         <v>1</v>
       </c>
       <c r="K187" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L187" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M187" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O187" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P187" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C188" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E188" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F188" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -10517,39 +10538,39 @@
         <v>1</v>
       </c>
       <c r="K188" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L188" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M188" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O188" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P188" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B189" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C189" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D189" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E189" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F189" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -10564,39 +10585,39 @@
         <v>1</v>
       </c>
       <c r="K189" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L189" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M189" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O189" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P189" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B190" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C190" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D190" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E190" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F190" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -10611,19 +10632,19 @@
         <v>1</v>
       </c>
       <c r="K190" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L190" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M190" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O190" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
